--- a/public/mla.updated.xlsx
+++ b/public/mla.updated.xlsx
@@ -1,40 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="510" windowWidth="28455" windowHeight="11955"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>mamata-banerjee.jpg</t>
+  </si>
+  <si>
+    <t>Posts consistent gains constituency-wide</t>
+  </si>
+  <si>
+    <t>suvendu-adhikari.jpg</t>
+  </si>
+  <si>
+    <t>Secures mandate with comfortable margin</t>
+  </si>
+  <si>
+    <t>firhad-hakim.jpg</t>
+  </si>
+  <si>
+    <t>Builds momentum across key booths</t>
+  </si>
+  <si>
+    <t>aroop-biswas.jpg</t>
+  </si>
+  <si>
+    <t>Maintains advantage through final round</t>
+  </si>
+  <si>
+    <t>babul-supriyo.jpg</t>
+  </si>
+  <si>
+    <t>bratya-basu.jpg</t>
+  </si>
+  <si>
+    <t>Wins with a strong local lead</t>
+  </si>
+  <si>
+    <t>shashi-panja.jpg</t>
+  </si>
+  <si>
+    <t>Registers decisive performance</t>
+  </si>
+  <si>
+    <t>manas-bhunia.jpg</t>
+  </si>
+  <si>
+    <t>agnimitra-paul.jpg</t>
+  </si>
+  <si>
+    <t>Takes early lead and holds firm</t>
+  </si>
+  <si>
+    <t>madan-mitra.jpg</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -397,99 +442,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="25.875" customWidth="1"/>
+    <col min="2" max="2" width="40.25" customWidth="1"/>
+    <col min="3" max="3" width="22.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>filename</v>
-      </c>
-      <c r="B1" t="str">
-        <v>text</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>mamata-banerjee.jpg</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Posts consistent gains constituency-wide</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>suvendu-adhikari.jpg</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Secures mandate with comfortable margin</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>firhad-hakim.jpg</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Builds momentum across key booths</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>aroop-biswas.jpg</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Maintains advantage through final round</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>babul-supriyo.jpg</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Builds momentum across key booths</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>bratya-basu.jpg</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Wins with a strong local lead</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>shashi-panja.jpg</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Registers decisive performance</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>manas-bhunia.jpg</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Posts consistent gains constituency-wide</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>agnimitra-paul.jpg</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Takes early lead and holds firm</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>madan-mitra.jpg</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Posts consistent gains constituency-wide</v>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError sqref="A1:C1 A11:B11 A2:B2 A3:B8 A9:B9 A10:B10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>